--- a/26-07-23_optowell_test2/t24.xlsx
+++ b/26-07-23_optowell_test2/t24.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dungeon\Desktop\Yuhang\26-07-18 optowell exp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dungeon\Desktop\Yuhang\26-07-22 optowell exp 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3938DB5D-A4C8-4962-A44A-A4D9D952CB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96785BB7-4F5E-40DB-89C9-A712C8BA59AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{DA241D28-DC64-4D6A-97B2-5AE29A167525}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{ECC1ECD8-06A1-496A-811D-54D37F87275C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>dungeon</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{1DE246AB-5DDF-4873-8EAC-4DDCBF8CF42E}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{37DE3AFB-0A86-4D95-BDCB-BB11501C6B95}">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{B71F6F96-E53A-4AC9-848F-4185AD509045}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{2787C5B3-C857-4A08-A4B0-46D9BA6E6E8E}">
       <text>
         <r>
           <rPr>
@@ -162,13 +162,13 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>19/07/2026</t>
+    <t>23/07/2026</t>
   </si>
   <si>
     <t>Time:</t>
   </si>
   <si>
-    <t>14:13:56</t>
+    <t>11:31:11</t>
   </si>
   <si>
     <t>System</t>
@@ -222,10 +222,10 @@
     <t>Start Time:</t>
   </si>
   <si>
-    <t>19/07/2026 14:13:56</t>
-  </si>
-  <si>
-    <t>Temperature: 37.6 °C</t>
+    <t>23/07/2026 11:31:11</t>
+  </si>
+  <si>
+    <t>Temperature: 27.9 °C</t>
   </si>
   <si>
     <t>&lt;&gt;</t>
@@ -258,7 +258,7 @@
     <t>End Time:</t>
   </si>
   <si>
-    <t>19/07/2026 14:15:17</t>
+    <t>23/07/2026 11:32:33</t>
   </si>
   <si>
     <t>Label: GFP 395nm</t>
@@ -294,25 +294,25 @@
     <t>Lag Time</t>
   </si>
   <si>
-    <t>19/07/2026 14:15:20</t>
-  </si>
-  <si>
-    <t>Temperature: 37.1 °C</t>
-  </si>
-  <si>
-    <t>19/07/2026 14:16:37</t>
+    <t>23/07/2026 11:32:35</t>
+  </si>
+  <si>
+    <t>Temperature: 28 °C</t>
+  </si>
+  <si>
+    <t>23/07/2026 11:33:53</t>
   </si>
   <si>
     <t>Label: GFP 480nm</t>
   </si>
   <si>
-    <t>19/07/2026 14:16:43</t>
-  </si>
-  <si>
-    <t>Temperature: 37.7 °C</t>
-  </si>
-  <si>
-    <t>19/07/2026 14:18:00</t>
+    <t>23/07/2026 11:33:58</t>
+  </si>
+  <si>
+    <t>Temperature: 28.1 °C</t>
+  </si>
+  <si>
+    <t>23/07/2026 11:35:16</t>
   </si>
 </sst>
 </file>
@@ -485,13 +485,13 @@
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Tecan.At.Excel.Attenuation" xfId="6" xr:uid="{D34C4A3D-39D8-4DA4-B166-3C40715F97D8}"/>
-    <cellStyle name="Tecan.At.Excel.AutoGain_0" xfId="7" xr:uid="{42134942-8BEB-4FAD-9DD2-939DE38FB219}"/>
-    <cellStyle name="Tecan.At.Excel.Error" xfId="1" xr:uid="{F50874FB-2360-4C8F-B305-633D4C315663}"/>
-    <cellStyle name="Tecan.At.Excel.GFactorAndMeasurementBlank" xfId="5" xr:uid="{C633A439-972E-4E96-8894-0909DBBBBD35}"/>
-    <cellStyle name="Tecan.At.Excel.GFactorBlank" xfId="3" xr:uid="{5A738E3B-D67B-4A36-AF60-6D22EF696CB3}"/>
-    <cellStyle name="Tecan.At.Excel.GFactorReference" xfId="4" xr:uid="{ECF3661A-2189-4B49-B222-5A739B7AE26C}"/>
-    <cellStyle name="Tecan.At.Excel.MeasurementBlank" xfId="2" xr:uid="{AD94A1BC-7B79-42AD-95CE-937D46539ED0}"/>
+    <cellStyle name="Tecan.At.Excel.Attenuation" xfId="6" xr:uid="{FD3EF278-FA7D-4D3E-8321-1EF2FB7422D0}"/>
+    <cellStyle name="Tecan.At.Excel.AutoGain_0" xfId="7" xr:uid="{EC079AD0-740A-4F91-B832-5BFCA0717DC9}"/>
+    <cellStyle name="Tecan.At.Excel.Error" xfId="1" xr:uid="{8C03C071-3A17-4C58-B079-584C76B47E7A}"/>
+    <cellStyle name="Tecan.At.Excel.GFactorAndMeasurementBlank" xfId="5" xr:uid="{EC25C0F3-073D-4E55-B444-A5FC042D8323}"/>
+    <cellStyle name="Tecan.At.Excel.GFactorBlank" xfId="3" xr:uid="{0DA58AED-7B52-43A8-A215-BCAC81DA15A6}"/>
+    <cellStyle name="Tecan.At.Excel.GFactorReference" xfId="4" xr:uid="{D5F96239-1FA9-4837-9832-F3970E31AC48}"/>
+    <cellStyle name="Tecan.At.Excel.MeasurementBlank" xfId="2" xr:uid="{E9F7054D-6187-49DD-9D82-804F3397853D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -822,7 +822,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{283DE7BC-E23C-4CB3-8037-6FC472E47337}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{138CF5D0-BF21-4497-853F-4F954306925C}">
   <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1011,40 +1011,40 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>0.41170001029968262</v>
+        <v>0.2460000067949295</v>
       </c>
       <c r="C25">
-        <v>0.41980001330375671</v>
+        <v>0.24330000579357147</v>
       </c>
       <c r="D25">
-        <v>0.41359999775886536</v>
+        <v>0.24959999322891235</v>
       </c>
       <c r="E25">
-        <v>0.32490000128746033</v>
+        <v>0.26230001449584961</v>
       </c>
       <c r="F25">
-        <v>0.37720000743865967</v>
+        <v>0.25740000605583191</v>
       </c>
       <c r="G25">
-        <v>0.36010000109672546</v>
+        <v>0.25920000672340393</v>
       </c>
       <c r="H25">
-        <v>0.43819999694824219</v>
+        <v>0.28880000114440918</v>
       </c>
       <c r="I25">
-        <v>0.44940000772476196</v>
+        <v>0.28709998726844788</v>
       </c>
       <c r="J25">
-        <v>0.4424000084400177</v>
+        <v>0.29269999265670776</v>
       </c>
       <c r="K25">
-        <v>0.41569998860359192</v>
+        <v>0.3734000027179718</v>
       </c>
       <c r="L25">
-        <v>0.42170000076293945</v>
+        <v>0.38479998707771301</v>
       </c>
       <c r="M25">
-        <v>0.41819998621940613</v>
+        <v>0.383899986743927</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -1052,40 +1052,40 @@
         <v>32</v>
       </c>
       <c r="B26">
-        <v>0.43599998950958252</v>
+        <v>0.25459998846054077</v>
       </c>
       <c r="C26">
-        <v>0.37040001153945923</v>
+        <v>0.25690001249313354</v>
       </c>
       <c r="D26">
-        <v>0.21439999341964722</v>
+        <v>0.25440001487731934</v>
       </c>
       <c r="E26">
-        <v>0.41019999980926514</v>
+        <v>0.26359999179840088</v>
       </c>
       <c r="F26">
-        <v>0.42680001258850098</v>
+        <v>0.25879999995231628</v>
       </c>
       <c r="G26">
-        <v>0.43569999933242798</v>
+        <v>0.26840001344680786</v>
       </c>
       <c r="H26">
-        <v>0.44490000605583191</v>
+        <v>0.28139999508857727</v>
       </c>
       <c r="I26">
-        <v>0.40230000019073486</v>
+        <v>0.27430000901222229</v>
       </c>
       <c r="J26">
-        <v>0.36649999022483826</v>
+        <v>0.28439998626708984</v>
       </c>
       <c r="K26">
-        <v>0.39710000157356262</v>
+        <v>0.36100000143051147</v>
       </c>
       <c r="L26">
-        <v>0.41760000586509705</v>
+        <v>0.37650001049041748</v>
       </c>
       <c r="M26">
-        <v>0.41159999370574951</v>
+        <v>0.38249999284744263</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -1093,40 +1093,40 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>0.19020000100135803</v>
+        <v>0.24950000643730164</v>
       </c>
       <c r="C27">
-        <v>0.40880000591278076</v>
+        <v>0.23659999668598175</v>
       </c>
       <c r="D27">
-        <v>0.42080000042915344</v>
+        <v>0.22900000214576721</v>
       </c>
       <c r="E27">
-        <v>0.42890000343322754</v>
+        <v>0.25639998912811279</v>
       </c>
       <c r="F27">
-        <v>0.42980000376701355</v>
+        <v>0.24040000140666962</v>
       </c>
       <c r="G27">
-        <v>0.40659999847412109</v>
+        <v>0.25799998641014099</v>
       </c>
       <c r="H27">
-        <v>0.35049998760223389</v>
+        <v>0.25859999656677246</v>
       </c>
       <c r="I27">
-        <v>0.33469998836517334</v>
+        <v>0.26629999279975891</v>
       </c>
       <c r="J27">
-        <v>0.39160001277923584</v>
+        <v>0.27090001106262207</v>
       </c>
       <c r="K27">
-        <v>0.42170000076293945</v>
+        <v>0.36030000448226929</v>
       </c>
       <c r="L27">
-        <v>0.42320001125335693</v>
+        <v>0.36509999632835388</v>
       </c>
       <c r="M27">
-        <v>0.41429999470710754</v>
+        <v>0.40669998526573181</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -1134,40 +1134,40 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>0.36039999127388</v>
+        <v>0.25949999690055847</v>
       </c>
       <c r="C28">
-        <v>0.34229999780654907</v>
+        <v>0.19910000264644623</v>
       </c>
       <c r="D28">
-        <v>0.38379999995231628</v>
+        <v>0.26499998569488525</v>
       </c>
       <c r="E28">
-        <v>0.45669999718666077</v>
+        <v>0.26350000500679016</v>
       </c>
       <c r="F28">
-        <v>0.42879998683929443</v>
+        <v>0.26190000772476196</v>
       </c>
       <c r="G28">
-        <v>0.39809998869895935</v>
+        <v>0.27549999952316284</v>
       </c>
       <c r="H28">
-        <v>0.49020001292228699</v>
+        <v>0.66949999332427979</v>
       </c>
       <c r="I28">
-        <v>0.33700001239776611</v>
+        <v>0.2784000039100647</v>
       </c>
       <c r="J28">
-        <v>0.37869998812675476</v>
+        <v>0.25209999084472656</v>
       </c>
       <c r="K28">
-        <v>0.43939998745918274</v>
+        <v>0.3409000039100647</v>
       </c>
       <c r="L28">
-        <v>0.43000000715255737</v>
+        <v>0.36520001292228699</v>
       </c>
       <c r="M28">
-        <v>0.42730000615119934</v>
+        <v>0.39259999990463257</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -1175,40 +1175,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>0.48269999027252197</v>
+        <v>0.30340000987052917</v>
       </c>
       <c r="C29">
-        <v>0.47830000519752502</v>
+        <v>0.31200000643730164</v>
       </c>
       <c r="D29">
-        <v>0.48449999094009399</v>
+        <v>0.31799998879432678</v>
       </c>
       <c r="E29">
-        <v>0.43180000782012939</v>
+        <v>0.31990000605583191</v>
       </c>
       <c r="F29">
-        <v>0.4325999915599823</v>
+        <v>0.31510001420974731</v>
       </c>
       <c r="G29">
-        <v>0.44049999117851257</v>
+        <v>0.47119998931884766</v>
       </c>
       <c r="H29">
-        <v>0.51239997148513794</v>
+        <v>0.34909999370574951</v>
       </c>
       <c r="I29">
-        <v>0.48510000109672546</v>
+        <v>0.32159999012947083</v>
       </c>
       <c r="J29">
-        <v>0.4593999981880188</v>
+        <v>0.29159998893737793</v>
       </c>
       <c r="K29">
-        <v>0.42890000343322754</v>
+        <v>0.35769999027252197</v>
       </c>
       <c r="L29">
-        <v>0.42879998683929443</v>
+        <v>0.37940001487731934</v>
       </c>
       <c r="M29">
-        <v>0.43140000104904175</v>
+        <v>0.40090000629425049</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -1216,40 +1216,40 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>0.476500004529953</v>
+        <v>0.33230000734329224</v>
       </c>
       <c r="C30">
-        <v>0.48050001263618469</v>
+        <v>0.33079999685287476</v>
       </c>
       <c r="D30">
-        <v>0.48759999871253967</v>
+        <v>0.32589998841285706</v>
       </c>
       <c r="E30">
-        <v>0.41290000081062317</v>
+        <v>0.33950001001358032</v>
       </c>
       <c r="F30">
-        <v>0.42980000376701355</v>
+        <v>0.33860000967979431</v>
       </c>
       <c r="G30">
-        <v>0.43119999766349792</v>
+        <v>0.34070000052452087</v>
       </c>
       <c r="H30">
-        <v>0.50340002775192261</v>
+        <v>0.33199998736381531</v>
       </c>
       <c r="I30">
-        <v>0.4950999915599823</v>
+        <v>0.33619999885559082</v>
       </c>
       <c r="J30">
-        <v>0.52549999952316284</v>
+        <v>0.3156999945640564</v>
       </c>
       <c r="K30">
-        <v>0.43709999322891235</v>
+        <v>0.36880001425743103</v>
       </c>
       <c r="L30">
-        <v>0.42930001020431519</v>
+        <v>0.40149998664855957</v>
       </c>
       <c r="M30">
-        <v>0.43549999594688416</v>
+        <v>0.40200001001358032</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -1257,40 +1257,40 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>0.47060000896453857</v>
+        <v>0.35479998588562012</v>
       </c>
       <c r="C31">
-        <v>0.4715999960899353</v>
+        <v>0.35420000553131104</v>
       </c>
       <c r="D31">
-        <v>0.47749999165534973</v>
+        <v>0.36629998683929443</v>
       </c>
       <c r="E31">
-        <v>0.47200000286102295</v>
+        <v>0.38780000805854797</v>
       </c>
       <c r="F31">
-        <v>0.47200000286102295</v>
+        <v>0.38679999113082886</v>
       </c>
       <c r="G31">
-        <v>0.47889998555183411</v>
+        <v>0.38989999890327454</v>
       </c>
       <c r="H31">
-        <v>0.50059998035430908</v>
+        <v>0.36250001192092896</v>
       </c>
       <c r="I31">
-        <v>0.47999998927116394</v>
+        <v>0.33730000257492065</v>
       </c>
       <c r="J31">
-        <v>0.46740001440048218</v>
+        <v>0.31549999117851257</v>
       </c>
       <c r="K31">
-        <v>0.43759998679161072</v>
+        <v>0.39959999918937683</v>
       </c>
       <c r="L31">
-        <v>0.43110001087188721</v>
+        <v>0.40529999136924744</v>
       </c>
       <c r="M31">
-        <v>0.42829999327659607</v>
+        <v>0.40709999203681946</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -1298,40 +1298,40 @@
         <v>38</v>
       </c>
       <c r="B32">
-        <v>0.47499999403953552</v>
+        <v>0.36329999566078186</v>
       </c>
       <c r="C32">
-        <v>0.48440000414848328</v>
+        <v>0.37569999694824219</v>
       </c>
       <c r="D32">
-        <v>0.47659999132156372</v>
+        <v>0.36640000343322754</v>
       </c>
       <c r="E32">
-        <v>0.46610000729560852</v>
+        <v>0.41159999370574951</v>
       </c>
       <c r="F32">
-        <v>0.47040000557899475</v>
+        <v>0.41490000486373901</v>
       </c>
       <c r="G32">
-        <v>0.48170000314712524</v>
+        <v>0.41809999942779541</v>
       </c>
       <c r="H32">
-        <v>0.48989999294281006</v>
+        <v>0.36700001358985901</v>
       </c>
       <c r="I32">
-        <v>0.46219998598098755</v>
+        <v>0.34940001368522644</v>
       </c>
       <c r="J32">
-        <v>0.46700000762939453</v>
+        <v>0.33289998769760132</v>
       </c>
       <c r="K32">
-        <v>0.43569999933242798</v>
+        <v>0.39879998564720154</v>
       </c>
       <c r="L32">
-        <v>0.4302000105381012</v>
+        <v>0.39980000257492065</v>
       </c>
       <c r="M32">
-        <v>0.43189999461174011</v>
+        <v>0.40880000591278076</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,40 +1510,40 @@
         <v>31</v>
       </c>
       <c r="B57">
-        <v>6822</v>
+        <v>527</v>
       </c>
       <c r="C57">
-        <v>7004</v>
+        <v>469</v>
       </c>
       <c r="D57">
-        <v>6898</v>
+        <v>460</v>
       </c>
       <c r="E57">
-        <v>2425</v>
+        <v>410</v>
       </c>
       <c r="F57">
-        <v>4488</v>
+        <v>346</v>
       </c>
       <c r="G57">
-        <v>3805</v>
+        <v>425</v>
       </c>
       <c r="H57">
-        <v>3358</v>
+        <v>833</v>
       </c>
       <c r="I57">
-        <v>1899</v>
+        <v>914</v>
       </c>
       <c r="J57">
-        <v>1893</v>
+        <v>953</v>
       </c>
       <c r="K57">
-        <v>2331</v>
+        <v>888</v>
       </c>
       <c r="L57">
-        <v>2401</v>
+        <v>1149</v>
       </c>
       <c r="M57">
-        <v>1894</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -1551,40 +1551,40 @@
         <v>32</v>
       </c>
       <c r="B58">
-        <v>4653</v>
+        <v>242</v>
       </c>
       <c r="C58">
-        <v>2838</v>
+        <v>239</v>
       </c>
       <c r="D58">
-        <v>735</v>
+        <v>1408</v>
       </c>
       <c r="E58">
-        <v>2020</v>
+        <v>406</v>
       </c>
       <c r="F58">
-        <v>2804</v>
+        <v>303</v>
       </c>
       <c r="G58">
-        <v>3279</v>
+        <v>329</v>
       </c>
       <c r="H58">
-        <v>1701</v>
+        <v>853</v>
       </c>
       <c r="I58">
-        <v>2211</v>
+        <v>943</v>
       </c>
       <c r="J58">
-        <v>1767</v>
+        <v>1017</v>
       </c>
       <c r="K58">
-        <v>1176</v>
+        <v>614</v>
       </c>
       <c r="L58">
-        <v>1233</v>
+        <v>747</v>
       </c>
       <c r="M58">
-        <v>1404</v>
+        <v>931</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -1592,40 +1592,40 @@
         <v>33</v>
       </c>
       <c r="B59">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C59">
-        <v>3859</v>
+        <v>214</v>
       </c>
       <c r="D59">
-        <v>3668</v>
+        <v>742</v>
       </c>
       <c r="E59">
-        <v>2785</v>
+        <v>202</v>
       </c>
       <c r="F59">
-        <v>3385</v>
+        <v>185</v>
       </c>
       <c r="G59">
-        <v>2390</v>
+        <v>197</v>
       </c>
       <c r="H59">
-        <v>1965</v>
+        <v>616</v>
       </c>
       <c r="I59">
-        <v>2253</v>
+        <v>620</v>
       </c>
       <c r="J59">
-        <v>3326</v>
+        <v>735</v>
       </c>
       <c r="K59">
-        <v>1029</v>
+        <v>516</v>
       </c>
       <c r="L59">
-        <v>1063</v>
+        <v>598</v>
       </c>
       <c r="M59">
-        <v>1053</v>
+        <v>841</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -1633,40 +1633,40 @@
         <v>34</v>
       </c>
       <c r="B60">
-        <v>4736</v>
+        <v>2560</v>
       </c>
       <c r="C60">
-        <v>4232</v>
+        <v>932</v>
       </c>
       <c r="D60">
-        <v>5562</v>
+        <v>1669</v>
       </c>
       <c r="E60">
-        <v>5494</v>
+        <v>1280</v>
       </c>
       <c r="F60">
-        <v>5534</v>
+        <v>1144</v>
       </c>
       <c r="G60">
-        <v>4906</v>
+        <v>1304</v>
       </c>
       <c r="H60">
-        <v>8945</v>
+        <v>840</v>
       </c>
       <c r="I60">
-        <v>1456</v>
+        <v>609</v>
       </c>
       <c r="J60">
-        <v>2516</v>
+        <v>653</v>
       </c>
       <c r="K60">
-        <v>787</v>
+        <v>469</v>
       </c>
       <c r="L60">
-        <v>946</v>
+        <v>569</v>
       </c>
       <c r="M60">
-        <v>927</v>
+        <v>755</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -1674,40 +1674,40 @@
         <v>35</v>
       </c>
       <c r="B61">
-        <v>9683</v>
+        <v>2526</v>
       </c>
       <c r="C61">
-        <v>10158</v>
+        <v>2326</v>
       </c>
       <c r="D61">
-        <v>10263</v>
+        <v>2073</v>
       </c>
       <c r="E61">
-        <v>6579</v>
+        <v>1643</v>
       </c>
       <c r="F61">
-        <v>6892</v>
+        <v>1544</v>
       </c>
       <c r="G61">
-        <v>7013</v>
+        <v>1612</v>
       </c>
       <c r="H61">
-        <v>11074</v>
+        <v>3172</v>
       </c>
       <c r="I61">
-        <v>6727</v>
+        <v>1067</v>
       </c>
       <c r="J61">
-        <v>1890</v>
+        <v>756</v>
       </c>
       <c r="K61">
-        <v>1307</v>
+        <v>567</v>
       </c>
       <c r="L61">
-        <v>1145</v>
+        <v>665</v>
       </c>
       <c r="M61">
-        <v>1064</v>
+        <v>908</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -1715,40 +1715,40 @@
         <v>36</v>
       </c>
       <c r="B62">
-        <v>9880</v>
+        <v>4194</v>
       </c>
       <c r="C62">
-        <v>10209</v>
+        <v>3299</v>
       </c>
       <c r="D62">
-        <v>10231</v>
+        <v>2681</v>
       </c>
       <c r="E62">
-        <v>5922</v>
+        <v>2334</v>
       </c>
       <c r="F62">
-        <v>6666</v>
+        <v>2159</v>
       </c>
       <c r="G62">
-        <v>6666</v>
+        <v>2321</v>
       </c>
       <c r="H62">
-        <v>11151</v>
+        <v>3865</v>
       </c>
       <c r="I62">
-        <v>8472</v>
+        <v>2111</v>
       </c>
       <c r="J62">
-        <v>3045</v>
+        <v>1108</v>
       </c>
       <c r="K62">
-        <v>1879</v>
+        <v>741</v>
       </c>
       <c r="L62">
-        <v>1445</v>
+        <v>872</v>
       </c>
       <c r="M62">
-        <v>1184</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -1756,40 +1756,40 @@
         <v>37</v>
       </c>
       <c r="B63">
-        <v>10262</v>
+        <v>7517</v>
       </c>
       <c r="C63">
-        <v>10338</v>
+        <v>6468</v>
       </c>
       <c r="D63">
-        <v>10506</v>
+        <v>6171</v>
       </c>
       <c r="E63">
-        <v>8573</v>
+        <v>5228</v>
       </c>
       <c r="F63">
-        <v>8747</v>
+        <v>5074</v>
       </c>
       <c r="G63">
-        <v>8858</v>
+        <v>5001</v>
       </c>
       <c r="H63">
-        <v>10831</v>
+        <v>4628</v>
       </c>
       <c r="I63">
-        <v>6895</v>
+        <v>1714</v>
       </c>
       <c r="J63">
-        <v>2675</v>
+        <v>1193</v>
       </c>
       <c r="K63">
-        <v>1869</v>
+        <v>1012</v>
       </c>
       <c r="L63">
-        <v>1448</v>
+        <v>1141</v>
       </c>
       <c r="M63">
-        <v>1267</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -1797,40 +1797,40 @@
         <v>38</v>
       </c>
       <c r="B64">
-        <v>10262</v>
+        <v>8183</v>
       </c>
       <c r="C64">
-        <v>10345</v>
+        <v>7268</v>
       </c>
       <c r="D64">
-        <v>10232</v>
+        <v>6043</v>
       </c>
       <c r="E64">
-        <v>8666</v>
+        <v>6045</v>
       </c>
       <c r="F64">
-        <v>8516</v>
+        <v>5937</v>
       </c>
       <c r="G64">
-        <v>8673</v>
+        <v>5813</v>
       </c>
       <c r="H64">
-        <v>10331</v>
+        <v>4450</v>
       </c>
       <c r="I64">
-        <v>5005</v>
+        <v>1673</v>
       </c>
       <c r="J64">
-        <v>2297</v>
+        <v>1301</v>
       </c>
       <c r="K64">
-        <v>1764</v>
+        <v>1398</v>
       </c>
       <c r="L64">
-        <v>1461</v>
+        <v>1263</v>
       </c>
       <c r="M64">
-        <v>1287</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2009,40 +2009,40 @@
         <v>31</v>
       </c>
       <c r="B89">
-        <v>6470</v>
+        <v>467</v>
       </c>
       <c r="C89">
-        <v>6623</v>
+        <v>418</v>
       </c>
       <c r="D89">
-        <v>6531</v>
+        <v>413</v>
       </c>
       <c r="E89">
-        <v>2245</v>
+        <v>368</v>
       </c>
       <c r="F89">
-        <v>4328</v>
+        <v>315</v>
       </c>
       <c r="G89">
-        <v>3614</v>
+        <v>388</v>
       </c>
       <c r="H89">
-        <v>3184</v>
+        <v>524</v>
       </c>
       <c r="I89">
-        <v>1732</v>
+        <v>599</v>
       </c>
       <c r="J89">
-        <v>1729</v>
+        <v>638</v>
       </c>
       <c r="K89">
-        <v>2109</v>
+        <v>684</v>
       </c>
       <c r="L89">
-        <v>2185</v>
+        <v>955</v>
       </c>
       <c r="M89">
-        <v>1692</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -2050,40 +2050,40 @@
         <v>32</v>
       </c>
       <c r="B90">
-        <v>4627</v>
+        <v>178</v>
       </c>
       <c r="C90">
-        <v>2881</v>
+        <v>180</v>
       </c>
       <c r="D90">
-        <v>715</v>
+        <v>1381</v>
       </c>
       <c r="E90">
-        <v>2000</v>
+        <v>359</v>
       </c>
       <c r="F90">
-        <v>2750</v>
+        <v>261</v>
       </c>
       <c r="G90">
-        <v>3220</v>
+        <v>268</v>
       </c>
       <c r="H90">
-        <v>1551</v>
+        <v>592</v>
       </c>
       <c r="I90">
-        <v>2031</v>
+        <v>741</v>
       </c>
       <c r="J90">
-        <v>1606</v>
+        <v>734</v>
       </c>
       <c r="K90">
-        <v>1025</v>
+        <v>387</v>
       </c>
       <c r="L90">
-        <v>1059</v>
+        <v>531</v>
       </c>
       <c r="M90">
-        <v>1193</v>
+        <v>746</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -2091,40 +2091,40 @@
         <v>33</v>
       </c>
       <c r="B91">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C91">
-        <v>3763</v>
+        <v>165</v>
       </c>
       <c r="D91">
-        <v>3588</v>
+        <v>760</v>
       </c>
       <c r="E91">
-        <v>2684</v>
+        <v>139</v>
       </c>
       <c r="F91">
-        <v>3259</v>
+        <v>139</v>
       </c>
       <c r="G91">
-        <v>2303</v>
+        <v>129</v>
       </c>
       <c r="H91">
-        <v>1856</v>
+        <v>406</v>
       </c>
       <c r="I91">
-        <v>2209</v>
+        <v>483</v>
       </c>
       <c r="J91">
-        <v>3209</v>
+        <v>550</v>
       </c>
       <c r="K91">
-        <v>859</v>
+        <v>283</v>
       </c>
       <c r="L91">
-        <v>903</v>
+        <v>375</v>
       </c>
       <c r="M91">
-        <v>888</v>
+        <v>621</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -2132,40 +2132,40 @@
         <v>34</v>
       </c>
       <c r="B92">
-        <v>4350</v>
+        <v>2235</v>
       </c>
       <c r="C92">
-        <v>3864</v>
+        <v>854</v>
       </c>
       <c r="D92">
-        <v>5154</v>
+        <v>1517</v>
       </c>
       <c r="E92">
-        <v>5152</v>
+        <v>1170</v>
       </c>
       <c r="F92">
-        <v>5340</v>
+        <v>1032</v>
       </c>
       <c r="G92">
-        <v>4572</v>
+        <v>1189</v>
       </c>
       <c r="H92">
-        <v>8281</v>
+        <v>625</v>
       </c>
       <c r="I92">
-        <v>1359</v>
+        <v>440</v>
       </c>
       <c r="J92">
-        <v>2412</v>
+        <v>490</v>
       </c>
       <c r="K92">
-        <v>636</v>
+        <v>249</v>
       </c>
       <c r="L92">
-        <v>779</v>
+        <v>354</v>
       </c>
       <c r="M92">
-        <v>780</v>
+        <v>566</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -2173,40 +2173,40 @@
         <v>35</v>
       </c>
       <c r="B93">
-        <v>9003</v>
+        <v>2263</v>
       </c>
       <c r="C93">
-        <v>9291</v>
+        <v>2075</v>
       </c>
       <c r="D93">
-        <v>9475</v>
+        <v>1872</v>
       </c>
       <c r="E93">
-        <v>6140</v>
+        <v>1540</v>
       </c>
       <c r="F93">
-        <v>6425</v>
+        <v>1444</v>
       </c>
       <c r="G93">
-        <v>6579</v>
+        <v>1503</v>
       </c>
       <c r="H93">
-        <v>10140</v>
+        <v>2805</v>
       </c>
       <c r="I93">
-        <v>6198</v>
+        <v>833</v>
       </c>
       <c r="J93">
-        <v>1730</v>
+        <v>533</v>
       </c>
       <c r="K93">
-        <v>1144</v>
+        <v>343</v>
       </c>
       <c r="L93">
-        <v>976</v>
+        <v>454</v>
       </c>
       <c r="M93">
-        <v>900</v>
+        <v>702</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -2214,40 +2214,40 @@
         <v>36</v>
       </c>
       <c r="B94">
-        <v>9018</v>
+        <v>3745</v>
       </c>
       <c r="C94">
-        <v>9297</v>
+        <v>2928</v>
       </c>
       <c r="D94">
-        <v>9370</v>
+        <v>2382</v>
       </c>
       <c r="E94">
-        <v>5504</v>
+        <v>2101</v>
       </c>
       <c r="F94">
-        <v>6193</v>
+        <v>1941</v>
       </c>
       <c r="G94">
-        <v>6241</v>
+        <v>2076</v>
       </c>
       <c r="H94">
-        <v>10195</v>
+        <v>3362</v>
       </c>
       <c r="I94">
-        <v>7811</v>
+        <v>1622</v>
       </c>
       <c r="J94">
-        <v>2903</v>
+        <v>863</v>
       </c>
       <c r="K94">
-        <v>1683</v>
+        <v>522</v>
       </c>
       <c r="L94">
-        <v>1274</v>
+        <v>667</v>
       </c>
       <c r="M94">
-        <v>963</v>
+        <v>841</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -2255,40 +2255,40 @@
         <v>37</v>
       </c>
       <c r="B95">
-        <v>9412</v>
+        <v>6752</v>
       </c>
       <c r="C95">
-        <v>9489</v>
+        <v>5749</v>
       </c>
       <c r="D95">
-        <v>9641</v>
+        <v>5403</v>
       </c>
       <c r="E95">
-        <v>7907</v>
+        <v>4686</v>
       </c>
       <c r="F95">
-        <v>8021</v>
+        <v>4530</v>
       </c>
       <c r="G95">
-        <v>8113</v>
+        <v>4465</v>
       </c>
       <c r="H95">
-        <v>9916</v>
+        <v>4021</v>
       </c>
       <c r="I95">
-        <v>6426</v>
+        <v>1442</v>
       </c>
       <c r="J95">
-        <v>2516</v>
+        <v>955</v>
       </c>
       <c r="K95">
-        <v>1698</v>
+        <v>770</v>
       </c>
       <c r="L95">
-        <v>1264</v>
+        <v>920</v>
       </c>
       <c r="M95">
-        <v>1110</v>
+        <v>951</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -2296,40 +2296,40 @@
         <v>38</v>
       </c>
       <c r="B96">
-        <v>9425</v>
+        <v>7399</v>
       </c>
       <c r="C96">
-        <v>9513</v>
+        <v>6508</v>
       </c>
       <c r="D96">
-        <v>9297</v>
+        <v>5349</v>
       </c>
       <c r="E96">
-        <v>7886</v>
+        <v>5491</v>
       </c>
       <c r="F96">
-        <v>7800</v>
+        <v>5378</v>
       </c>
       <c r="G96">
-        <v>7927</v>
+        <v>5236</v>
       </c>
       <c r="H96">
-        <v>9431</v>
+        <v>3891</v>
       </c>
       <c r="I96">
-        <v>4670</v>
+        <v>1391</v>
       </c>
       <c r="J96">
-        <v>2151</v>
+        <v>1058</v>
       </c>
       <c r="K96">
-        <v>1558</v>
+        <v>1203</v>
       </c>
       <c r="L96">
-        <v>1294</v>
+        <v>1037</v>
       </c>
       <c r="M96">
-        <v>1111</v>
+        <v>981</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2347,7 +2347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A9D141-08B4-4748-A821-A5AEF30FF9E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B86F4FC-BE8E-4ABC-BB72-DBD14760BC7A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
